--- a/data/trans_orig/IP16A10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>430</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3732</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>11439</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14724</t>
+          <t>14741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18338</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31550</t>
+          <t>31116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36113</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>15616</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32969</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>18586</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27317</t>
+          <t>27813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32391</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>4445</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35159</t>
+          <t>34653</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71236</t>
+          <t>71080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75868</t>
+          <t>75863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14962</t>
+          <t>15593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>39010</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>14,0%</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14922</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>86,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14742</t>
+          <t>14637</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98532</t>
+          <t>98272</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>106095</t>
+          <t>105881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>128558</t>
+          <t>128427</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134626</t>
+          <t>134611</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230288</t>
+          <t>230393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239187</t>
+          <t>239596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2732</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24071</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48453</t>
+          <t>47445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13342</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>509</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5944</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>912</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>54683</t>
+          <t>54533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59973</t>
+          <t>59968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68799</t>
+          <t>69400</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125655</t>
+          <t>125311</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131670</t>
+          <t>131690</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28368</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65921</t>
+          <t>65785</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10574</t>
+          <t>10643</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7358</t>
+          <t>7788</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>171063</t>
+          <t>170917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>177045</t>
+          <t>177114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>170520</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>177060</t>
+          <t>177054</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>343861</t>
+          <t>344944</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>353171</t>
+          <t>353247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36595</t>
+          <t>36906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41771</t>
+          <t>41785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52495</t>
+          <t>52220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>39445</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94299</t>
+          <t>94990</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98994</t>
+          <t>99008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,47 +8110,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>3824</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>8336</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>3824</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>8370</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>151613</t>
+          <t>151712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>155823</t>
+          <t>156377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>134183</t>
+          <t>134314</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139732</t>
+          <t>139742</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,47 +8223,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>434</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>292946</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>288434</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>295375</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>99,53%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>292946</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>288400</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>295481</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A10-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3128</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1488</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3732</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3810</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3124</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>5383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20777</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18334</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13683</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11439</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14741</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>11361</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14736</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,19%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20777</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18338</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31116</t>
+          <t>31250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>36104</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,107 +1065,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1233</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3814</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3805</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,35%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3861</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1233</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4333</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1183,69 +1183,69 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>18197</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15616</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>15625</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,65%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>80,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>80,42%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>54</t>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>33426</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3076</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1765</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4315</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,89%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3366</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21285</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18876</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>85,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>9345</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>6795</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10604</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>6866</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,11%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21285</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>18586</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,96%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,01%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1266</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3931</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4136</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5395</t>
+          <t>5585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38064</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34697</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>36419</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>33240</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>33754</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,64%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>89,57%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38064</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34653</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,34%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>111</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71080</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75863</t>
+          <t>75852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1044</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3661</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,54%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>19,42%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1044</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3284</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1044</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3742</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>17809</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>15593</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>15192</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,46%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>82,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>80,58%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>62</t>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39010</t>
+          <t>39468</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,107 +2437,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>28,24%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>642</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2656</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2801</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>10695</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8136</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>71,76%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>10695</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>8681</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>94,34%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3853</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11462</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3779</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>11532</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>6,19%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6870</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14637</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>132578</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>129112</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>134634</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>102937</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>98272</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>105881</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>98202</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>105955</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>93,81%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>89,55%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>132578</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>128427</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>134611</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230393</t>
+          <t>230411</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>239596</t>
+          <t>239545</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,107 +3357,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3085</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3254</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3218</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4312</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -3470,74 +3470,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26158</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23718</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23549</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,59%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>72</t>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47445</t>
+          <t>48539</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>24953</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>26803</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>24953</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>25619</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>14901</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>25619</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>14901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,107 +4043,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>627</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3004</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2766</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,93%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,82%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,33%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3203</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -4156,74 +4156,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15334</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12957</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13195</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,07%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,18%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,67%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>49</t>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30981</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18223</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>15961</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>18223</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3379</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5853</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,83%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71473</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>68746</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>72125</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>58453</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54533</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>59968</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>54624</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>59971</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,17%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,32%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,16%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>71473</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>69400</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>72125</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>184</t>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125311</t>
+          <t>125826</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>131690</t>
+          <t>131948</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72125</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72125</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72125</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>60477</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>72125</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>72125</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>72125</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,107 +4729,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4932</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>14,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1540</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5444</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32090</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28698</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>85,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>32090</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>28323</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>65785</t>
+          <t>65663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33630</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>37598</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>33630</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,107 +5072,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3889</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>26,87%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1252</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3833</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3949</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>4,77%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>26,48%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1252</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4232</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13224</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>10587</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,13%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13224</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>10643</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>11795</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>14476</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5420,67 +5420,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>3445</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1269</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7555</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>7337</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1135</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>7610</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>3445</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>7788</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11618</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>174863</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>170753</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>177039</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>174958</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>170917</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>177114</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>170644</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>177119</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,15%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>95,73%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,36%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>247</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>174863</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>170520</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>177054</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,07%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>499</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>344944</t>
+          <t>345010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>353247</t>
+          <t>353266</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>178308</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>178308</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>178308</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>178254</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>178308</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>178308</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>178308</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>18999</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21028</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>18999</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21028</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>17,94%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3335</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,05%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4168</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,12%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -6448,74 +6448,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20898</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>18268</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,06%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16973</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16795</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,95%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>83,43%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>20898</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>18093</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,88%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>81,28%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36906</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>41785</t>
+          <t>41786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>20130</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>22261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6796,42 +6796,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6909,52 +6909,52 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11778</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11883</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>11778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1149</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4341</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3552</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42297</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>39572</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>55412</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>52220</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>52458</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>42297</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>39445</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,74%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>148</t>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94990</t>
+          <t>94728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99008</t>
+          <t>99009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42997</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>56561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>42997</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>35779</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>30245</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>35779</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>30245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>12086</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8055,67 +8055,67 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>1762</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4665</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6080</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1395</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>138332</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>135331</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>139739</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>96,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,53%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>154615</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>151712</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>156377</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>151054</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>155813</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>138332</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>134314</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>139742</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,53%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>288434</t>
+          <t>288724</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>295375</t>
+          <t>295444</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140394</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>156377</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>140394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
